--- a/ExcelData/Table.xlsx
+++ b/ExcelData/Table.xlsx
@@ -12,15 +12,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>编号ID</t>
-  </si>
-  <si>
-    <t>名字NAME</t>
-  </si>
-  <si>
-    <t>描述DESC</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>DESC</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <t>int</t>
@@ -32,16 +41,25 @@
     <t>string[]</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>苹果</t>
   </si>
   <si>
     <t>红色#甜</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>香蕉</t>
   </si>
   <si>
     <t>黄色#甜</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>橘子</t>
@@ -55,8 +73,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -81,8 +104,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -93,67 +122,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.95548439025879" customWidth="1"/>
-    <col min="3" max="3" width="9.75227832794189" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>11</v>
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
